--- a/VerveStacks_MYS_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_MYS_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_MYS_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{46EA87D6-989E-4B1B-8D67-15CCE6F7988F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3E4CD84A-5B92-4EA6-8EC8-C69B9F460510}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11295" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="misc" sheetId="7" r:id="rId1"/>
@@ -901,18 +901,114 @@
     <t>daynite</t>
   </si>
   <si>
+    <t>distr_solelc_spv_MYS_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MYS_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MYS_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MYS_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MYS_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_MYS_004</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 4</t>
   </si>
   <si>
+    <t>distr_solelc_spv_MYS_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MYS_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MYS_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MYS_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MYS_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_MYS_003</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 3</t>
   </si>
   <si>
+    <t>distr_solelc_spv_MYS_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MYS_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MYS_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MYS_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MYS_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MYS_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_MYS_018</t>
   </si>
   <si>
@@ -931,48 +1027,6 @@
     <t>connecting solar to buses in cluster 16</t>
   </si>
   <si>
-    <t>distr_solelc_spv_MYS_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MYS_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MYS_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MYS_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MYS_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MYS_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MYS_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_MYS_022</t>
   </si>
   <si>
@@ -985,60 +1039,6 @@
     <t>connecting solar to buses in cluster 8</t>
   </si>
   <si>
-    <t>distr_solelc_spv_MYS_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MYS_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MYS_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MYS_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MYS_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MYS_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MYS_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MYS_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MYS_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
@@ -1048,12 +1048,60 @@
     <t>e_w320730394-275_MYS,e_MY5-275_MYS,e_MY4-275_MYS,e_w755391602-275_MYS</t>
   </si>
   <si>
+    <t>e_w554295894-275_MYS,e_w554938963-275_MYS,e_w553339782-275_MYS,e_w445431079-275_MYS,e_w1137308780-500_MYS,e_w755668283-500_MYS,e_w755668283-275_MYS,e_w235501402-500_MYS,e_MY63-275_MYS</t>
+  </si>
+  <si>
+    <t>e_MY59-275_MYS,e_w1137665620-500_MYS</t>
+  </si>
+  <si>
+    <t>e_w691239971-275_MYS,e_w399307646-275_MYS,e_MY68-275_MYS,e_w320246940-275_MYS,e_w934653890-275_MYS</t>
+  </si>
+  <si>
+    <t>e_w561806959-275_MYS,e_w235966081-275_MYS,e_w399307647-275_MYS,e_w1137665609-275_MYS</t>
+  </si>
+  <si>
+    <t>e_MY59-275_MYS</t>
+  </si>
+  <si>
     <t>e_w691200886-275_MYS,e_w235943019-275_MYS,e_w235951698-275_MYS,e_w691239971-275_MYS,e_w325835238-275_MYS,e_MY68-275_MYS</t>
   </si>
   <si>
+    <t>e_w286559638-275_MYS,e_w326097227-275_MYS,e_w286559640-275_MYS,e_MY2-275_MYS</t>
+  </si>
+  <si>
+    <t>e_w755391602-275_MYS,e_MY17-275_MYS,e_MY3-275_MYS,e_w552820941-275_MYS,e_w552681748-275_MYS,e_MY18-275_MYS,e_w755700380-275_MYS,e_w552780098-275_MYS</t>
+  </si>
+  <si>
+    <t>e_w328415531-275_MYS</t>
+  </si>
+  <si>
+    <t>e_w492388990-275_MYS,e_MY46-275_MYS,e_MY61-275_MYS,e_MY52-275_MYS,e_w1137308780-275_MYS,e_w553040556-275_MYS,e_w1137308780-500_MYS</t>
+  </si>
+  <si>
+    <t>e_MY25-500_MYS,e_w1137665617-275_MYS,e_w1137665620-500_MYS,e_w513950834-275_MYS</t>
+  </si>
+  <si>
     <t>e_w1324718458-275_MYS,e_MY20-275_MYS,e_MY13-275_MYS,e_w460916219-275_MYS,e_w316035698-500_MYS,e_MY21-275_MYS,e_MY14-275_MYS,e_w556802417-275_MYS</t>
   </si>
   <si>
+    <t>e_w553040556-275_MYS,e_w662315251-275_MYS,e_w892365043-275_MYS,e_MY18-275_MYS</t>
+  </si>
+  <si>
+    <t>e_w691633793-275_MYS,e_w691633796-275_MYS,e_w513610290-275_MYS,e_w236051516-275_MYS,e_w1137665615-275_MYS</t>
+  </si>
+  <si>
+    <t>e_w320246940-275_MYS,e_w934653890-275_MYS,e_w513610290-275_MYS</t>
+  </si>
+  <si>
+    <t>e_w552579228-275_MYS,e_w316035705-500_MYS,e_w552589219-275_MYS,e_MY27-275_MYS</t>
+  </si>
+  <si>
+    <t>e_w1137308780-500_MYS,e_w559750680-275_MYS,e_w396464338-275_MYS,e_w235501402-500_MYS,e_w496114385-275_MYS</t>
+  </si>
+  <si>
+    <t>e_MY16-275_MYS,e_MY12-275_MYS,e_w450080688-275_MYS,e_w328415531-275_MYS</t>
+  </si>
+  <si>
     <t>e_w235851822-500_MYS,e_MY64-275_MYS,e_MY76-275_MYS,e_w755608493-275_MYS,e_w496114385-275_MYS</t>
   </si>
   <si>
@@ -1063,58 +1111,34 @@
     <t>e_w450080688-275_MYS,e_w328415531-275_MYS</t>
   </si>
   <si>
-    <t>e_w320246940-275_MYS,e_w934653890-275_MYS,e_w513610290-275_MYS</t>
-  </si>
-  <si>
-    <t>e_w554295894-275_MYS,e_w554938963-275_MYS,e_w553339782-275_MYS,e_w445431079-275_MYS,e_w1137308780-500_MYS,e_w755668283-500_MYS,e_w755668283-275_MYS,e_w235501402-500_MYS,e_MY63-275_MYS</t>
-  </si>
-  <si>
-    <t>e_w691239971-275_MYS,e_w399307646-275_MYS,e_MY68-275_MYS,e_w320246940-275_MYS,e_w934653890-275_MYS</t>
-  </si>
-  <si>
-    <t>e_w561806959-275_MYS,e_w235966081-275_MYS,e_w399307647-275_MYS,e_w1137665609-275_MYS</t>
-  </si>
-  <si>
-    <t>e_MY59-275_MYS</t>
-  </si>
-  <si>
-    <t>e_MY16-275_MYS,e_MY12-275_MYS,e_w450080688-275_MYS,e_w328415531-275_MYS</t>
-  </si>
-  <si>
-    <t>e_MY59-275_MYS,e_w1137665620-500_MYS</t>
-  </si>
-  <si>
     <t>e_MY27-275_MYS,e_w755036990-275_MYS,e_w317124038-275_MYS,e_MY26-275_MYS,e_w885845346-275_MYS,e_w662315251-275_MYS</t>
   </si>
   <si>
     <t>e_w1137665620-500_MYS,e_w513950834-275_MYS,e_w1285211558-275_MYS,e_MY16-275_MYS</t>
   </si>
   <si>
-    <t>e_w553040556-275_MYS,e_w662315251-275_MYS,e_w892365043-275_MYS,e_MY18-275_MYS</t>
-  </si>
-  <si>
-    <t>e_w691633793-275_MYS,e_w691633796-275_MYS,e_w513610290-275_MYS,e_w236051516-275_MYS,e_w1137665615-275_MYS</t>
-  </si>
-  <si>
-    <t>e_w552579228-275_MYS,e_w316035705-500_MYS,e_w552589219-275_MYS,e_MY27-275_MYS</t>
-  </si>
-  <si>
-    <t>e_w1137308780-500_MYS,e_w559750680-275_MYS,e_w396464338-275_MYS,e_w235501402-500_MYS,e_w496114385-275_MYS</t>
-  </si>
-  <si>
-    <t>e_w286559638-275_MYS,e_w326097227-275_MYS,e_w286559640-275_MYS,e_MY2-275_MYS</t>
-  </si>
-  <si>
-    <t>e_w755391602-275_MYS,e_MY17-275_MYS,e_MY3-275_MYS,e_w552820941-275_MYS,e_w552681748-275_MYS,e_MY18-275_MYS,e_w755700380-275_MYS,e_w552780098-275_MYS</t>
-  </si>
-  <si>
-    <t>e_w328415531-275_MYS</t>
-  </si>
-  <si>
-    <t>e_w492388990-275_MYS,e_MY46-275_MYS,e_MY61-275_MYS,e_MY52-275_MYS,e_w1137308780-275_MYS,e_w553040556-275_MYS,e_w1137308780-500_MYS</t>
-  </si>
-  <si>
-    <t>e_MY25-500_MYS,e_w1137665617-275_MYS,e_w1137665620-500_MYS,e_w513950834-275_MYS</t>
+    <t>distr_wonelc_won_MYS_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_MYS_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_MYS_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_MYS_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
   </si>
   <si>
     <t>distr_wonelc_won_MYS_003</t>
@@ -1123,10 +1147,10 @@
     <t>connecting wind onshore to buses in cluster 3</t>
   </si>
   <si>
-    <t>distr_wonelc_won_MYS_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
+    <t>distr_wonelc_won_MYS_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
   </si>
   <si>
     <t>distr_wonelc_won_MYS_010</t>
@@ -1153,40 +1177,34 @@
     <t>connecting wind onshore to buses in cluster 5</t>
   </si>
   <si>
-    <t>distr_wonelc_won_MYS_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_MYS_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_MYS_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_MYS_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
+    <t>elc_won_MYS_009</t>
+  </si>
+  <si>
+    <t>e_w235501402-500_MYS,e_w559750680-275_MYS,e_w496114385-275_MYS</t>
+  </si>
+  <si>
+    <t>elc_won_MYS_007</t>
+  </si>
+  <si>
+    <t>e_w286559638-275_MYS</t>
+  </si>
+  <si>
+    <t>elc_won_MYS_002</t>
+  </si>
+  <si>
+    <t>e_w450080688-275_MYS</t>
+  </si>
+  <si>
+    <t>elc_won_MYS_004</t>
+  </si>
+  <si>
+    <t>e_w755608493-275_MYS,e_w496114385-275_MYS,e_MY76-275_MYS</t>
   </si>
   <si>
     <t>elc_won_MYS_003</t>
   </si>
   <si>
-    <t>e_w450080688-275_MYS</t>
-  </si>
-  <si>
-    <t>elc_won_MYS_004</t>
-  </si>
-  <si>
-    <t>e_w755608493-275_MYS,e_w496114385-275_MYS,e_MY76-275_MYS</t>
+    <t>elc_won_MYS_006</t>
   </si>
   <si>
     <t>elc_won_MYS_010</t>
@@ -1210,22 +1228,28 @@
     <t>e_w235851822-500_MYS,e_MY76-275_MYS</t>
   </si>
   <si>
-    <t>elc_won_MYS_007</t>
-  </si>
-  <si>
-    <t>e_w286559638-275_MYS</t>
-  </si>
-  <si>
-    <t>elc_won_MYS_002</t>
-  </si>
-  <si>
-    <t>elc_won_MYS_006</t>
-  </si>
-  <si>
-    <t>elc_won_MYS_009</t>
-  </si>
-  <si>
-    <t>e_w235501402-500_MYS,e_w559750680-275_MYS,e_w496114385-275_MYS</t>
+    <t>distr_wofelc_wof_MYS_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_MYS_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_MYS_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_MYS_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
   </si>
   <si>
     <t>distr_wofelc_wof_MYS_008</t>
@@ -1240,30 +1264,6 @@
     <t>connecting wind offshore to buses in cluster 6</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_MYS_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_MYS_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_MYS_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_MYS_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_MYS_003</t>
   </si>
   <si>
@@ -1288,6 +1288,24 @@
     <t>connecting wind offshore to buses in cluster 5</t>
   </si>
   <si>
+    <t>elc_wof_MYS_007</t>
+  </si>
+  <si>
+    <t>e_w513950834-275_MYS</t>
+  </si>
+  <si>
+    <t>elc_wof_MYS_009</t>
+  </si>
+  <si>
+    <t>elc_wof_MYS_002</t>
+  </si>
+  <si>
+    <t>e_w552780098-275_MYS</t>
+  </si>
+  <si>
+    <t>elc_wof_MYS_004</t>
+  </si>
+  <si>
     <t>elc_wof_MYS_008</t>
   </si>
   <si>
@@ -1295,24 +1313,6 @@
   </si>
   <si>
     <t>elc_wof_MYS_006</t>
-  </si>
-  <si>
-    <t>elc_wof_MYS_007</t>
-  </si>
-  <si>
-    <t>e_w513950834-275_MYS</t>
-  </si>
-  <si>
-    <t>elc_wof_MYS_009</t>
-  </si>
-  <si>
-    <t>elc_wof_MYS_002</t>
-  </si>
-  <si>
-    <t>e_w552780098-275_MYS</t>
-  </si>
-  <si>
-    <t>elc_wof_MYS_004</t>
   </si>
   <si>
     <t>elc_wof_MYS_003</t>
@@ -6464,7 +6464,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{774103AB-D3C1-44A5-B2AF-EB3647BDF93F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35D19764-7898-4056-B370-AB1D226D06B7}">
   <dimension ref="B9:BD34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -6744,10 +6744,10 @@
         <v>350</v>
       </c>
       <c r="AO11">
-        <v>0.99351413211341089</v>
+        <v>0.99280840617902688</v>
       </c>
       <c r="AP11">
-        <v>118.90757792080102</v>
+        <v>131.84588671784124</v>
       </c>
       <c r="AR11" t="s">
         <v>252</v>
@@ -6780,10 +6780,10 @@
         <v>387</v>
       </c>
       <c r="BC11">
-        <v>0.97644633349267118</v>
+        <v>0.98322281233462283</v>
       </c>
       <c r="BD11">
-        <v>431.81721930102793</v>
+        <v>307.58177386524892</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -6848,16 +6848,16 @@
         <v>257</v>
       </c>
       <c r="Y12" t="s">
-        <v>230</v>
+        <v>245</v>
       </c>
       <c r="Z12" t="s">
         <v>306</v>
       </c>
       <c r="AA12">
-        <v>0.99742391546858211</v>
+        <v>0.99800680362584671</v>
       </c>
       <c r="AB12">
-        <v>47.228216409328219</v>
+        <v>36.541933526143403</v>
       </c>
       <c r="AD12" t="s">
         <v>252</v>
@@ -6890,10 +6890,10 @@
         <v>352</v>
       </c>
       <c r="AO12">
-        <v>0.99774058703572632</v>
+        <v>0.99806527403456324</v>
       </c>
       <c r="AP12">
-        <v>41.422571011684674</v>
+        <v>35.469976033007349</v>
       </c>
       <c r="AR12" t="s">
         <v>252</v>
@@ -6923,13 +6923,13 @@
         <v>388</v>
       </c>
       <c r="BB12" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="BC12">
-        <v>0.98985596153199862</v>
+        <v>0.98051979717181825</v>
       </c>
       <c r="BD12">
-        <v>185.97403858002539</v>
+        <v>357.13705184999884</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -6994,16 +6994,16 @@
         <v>259</v>
       </c>
       <c r="Y13" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="Z13" t="s">
         <v>307</v>
       </c>
       <c r="AA13">
-        <v>0.99923097127788529</v>
+        <v>0.99575198492146944</v>
       </c>
       <c r="AB13">
-        <v>14.098859905436759</v>
+        <v>77.880276439726259</v>
       </c>
       <c r="AD13" t="s">
         <v>252</v>
@@ -7036,10 +7036,10 @@
         <v>354</v>
       </c>
       <c r="AO13">
-        <v>0.99576941373570749</v>
+        <v>0.99576055143223485</v>
       </c>
       <c r="AP13">
-        <v>77.560748178695945</v>
+        <v>77.723223742361768</v>
       </c>
       <c r="AR13" t="s">
         <v>252</v>
@@ -7072,10 +7072,10 @@
         <v>390</v>
       </c>
       <c r="BC13">
-        <v>0.98322281233462283</v>
+        <v>0.98500048755641589</v>
       </c>
       <c r="BD13">
-        <v>307.58177386524892</v>
+        <v>274.9910614657079</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -7140,16 +7140,16 @@
         <v>261</v>
       </c>
       <c r="Y14" t="s">
-        <v>244</v>
+        <v>231</v>
       </c>
       <c r="Z14" t="s">
         <v>308</v>
       </c>
       <c r="AA14">
-        <v>0.99858790335879577</v>
+        <v>0.99858320886855523</v>
       </c>
       <c r="AB14">
-        <v>25.888438422076831</v>
+        <v>25.974504076486607</v>
       </c>
       <c r="AD14" t="s">
         <v>252</v>
@@ -7182,10 +7182,10 @@
         <v>356</v>
       </c>
       <c r="AO14">
-        <v>0.99874285064295787</v>
+        <v>0.99774058703572632</v>
       </c>
       <c r="AP14">
-        <v>23.047738212439921</v>
+        <v>41.422571011684674</v>
       </c>
       <c r="AR14" t="s">
         <v>252</v>
@@ -7215,13 +7215,13 @@
         <v>391</v>
       </c>
       <c r="BB14" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="BC14">
-        <v>0.98051979717181825</v>
+        <v>0.9926406959075802</v>
       </c>
       <c r="BD14">
-        <v>357.13705184999884</v>
+        <v>134.92057502769742</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -7286,16 +7286,16 @@
         <v>263</v>
       </c>
       <c r="Y15" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Z15" t="s">
         <v>309</v>
       </c>
       <c r="AA15">
-        <v>0.99832758042474679</v>
+        <v>0.9980999989767797</v>
       </c>
       <c r="AB15">
-        <v>30.661025546308895</v>
+        <v>34.833352092372579</v>
       </c>
       <c r="AD15" t="s">
         <v>252</v>
@@ -7325,13 +7325,13 @@
         <v>357</v>
       </c>
       <c r="AN15" t="s">
-        <v>326</v>
+        <v>354</v>
       </c>
       <c r="AO15">
-        <v>0.99028422987608544</v>
+        <v>0.99351413211341089</v>
       </c>
       <c r="AP15">
-        <v>178.1224522717672</v>
+        <v>118.90757792080102</v>
       </c>
       <c r="AR15" t="s">
         <v>252</v>
@@ -7364,10 +7364,10 @@
         <v>393</v>
       </c>
       <c r="BC15">
-        <v>0.98500048755641589</v>
+        <v>0.97644633349267118</v>
       </c>
       <c r="BD15">
-        <v>274.9910614657079</v>
+        <v>431.81721930102793</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -7432,16 +7432,16 @@
         <v>265</v>
       </c>
       <c r="Y16" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="Z16" t="s">
         <v>310</v>
       </c>
       <c r="AA16">
-        <v>0.99610860481200558</v>
+        <v>0.99467655833764279</v>
       </c>
       <c r="AB16">
-        <v>71.342245113231982</v>
+        <v>97.596430476549543</v>
       </c>
       <c r="AD16" t="s">
         <v>252</v>
@@ -7471,13 +7471,13 @@
         <v>358</v>
       </c>
       <c r="AN16" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="AO16">
-        <v>0.99864191583933049</v>
+        <v>0.99834719992221588</v>
       </c>
       <c r="AP16">
-        <v>24.898209612275185</v>
+        <v>30.301334759374811</v>
       </c>
       <c r="AR16" t="s">
         <v>252</v>
@@ -7507,13 +7507,13 @@
         <v>394</v>
       </c>
       <c r="BB16" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="BC16">
-        <v>0.9926406959075802</v>
+        <v>0.98985596153199862</v>
       </c>
       <c r="BD16">
-        <v>134.92057502769742</v>
+        <v>185.97403858002539</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -7578,16 +7578,16 @@
         <v>267</v>
       </c>
       <c r="Y17" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="Z17" t="s">
         <v>311</v>
       </c>
       <c r="AA17">
-        <v>0.9940167733084464</v>
+        <v>0.99742391546858211</v>
       </c>
       <c r="AB17">
-        <v>109.69248934514933</v>
+        <v>47.228216409328219</v>
       </c>
       <c r="AD17" t="s">
         <v>252</v>
@@ -7614,16 +7614,16 @@
         <v>341</v>
       </c>
       <c r="AM17" t="s">
+        <v>359</v>
+      </c>
+      <c r="AN17" t="s">
         <v>360</v>
       </c>
-      <c r="AN17" t="s">
-        <v>361</v>
-      </c>
       <c r="AO17">
-        <v>0.99806527403456324</v>
+        <v>0.99576941373570749</v>
       </c>
       <c r="AP17">
-        <v>35.469976033007349</v>
+        <v>77.560748178695945</v>
       </c>
       <c r="AR17" t="s">
         <v>252</v>
@@ -7724,16 +7724,16 @@
         <v>269</v>
       </c>
       <c r="Y18" t="s">
-        <v>245</v>
+        <v>228</v>
       </c>
       <c r="Z18" t="s">
         <v>312</v>
       </c>
       <c r="AA18">
-        <v>0.99800680362584671</v>
+        <v>0.99799805381298523</v>
       </c>
       <c r="AB18">
-        <v>36.541933526143403</v>
+        <v>36.70234676193683</v>
       </c>
       <c r="AD18" t="s">
         <v>252</v>
@@ -7760,16 +7760,16 @@
         <v>343</v>
       </c>
       <c r="AM18" t="s">
+        <v>361</v>
+      </c>
+      <c r="AN18" t="s">
         <v>362</v>
       </c>
-      <c r="AN18" t="s">
-        <v>350</v>
-      </c>
       <c r="AO18">
-        <v>0.99576055143223485</v>
+        <v>0.99874285064295787</v>
       </c>
       <c r="AP18">
-        <v>77.723223742361768</v>
+        <v>23.047738212439921</v>
       </c>
       <c r="AR18" t="s">
         <v>252</v>
@@ -7870,16 +7870,16 @@
         <v>271</v>
       </c>
       <c r="Y19" t="s">
-        <v>231</v>
+        <v>250</v>
       </c>
       <c r="Z19" t="s">
         <v>313</v>
       </c>
       <c r="AA19">
-        <v>0.99858320886855523</v>
+        <v>0.9980696486807239</v>
       </c>
       <c r="AB19">
-        <v>25.974504076486607</v>
+        <v>35.389774186729234</v>
       </c>
       <c r="AD19" t="s">
         <v>252</v>
@@ -7909,13 +7909,13 @@
         <v>363</v>
       </c>
       <c r="AN19" t="s">
-        <v>361</v>
+        <v>314</v>
       </c>
       <c r="AO19">
-        <v>0.99834719992221588</v>
+        <v>0.99028422987608544</v>
       </c>
       <c r="AP19">
-        <v>30.301334759374811</v>
+        <v>178.1224522717672</v>
       </c>
       <c r="AR19" t="s">
         <v>252</v>
@@ -8016,16 +8016,16 @@
         <v>273</v>
       </c>
       <c r="Y20" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="Z20" t="s">
         <v>314</v>
       </c>
       <c r="AA20">
-        <v>0.9980999989767797</v>
+        <v>0.99314549576336597</v>
       </c>
       <c r="AB20">
-        <v>34.833352092372579</v>
+        <v>125.66591100495808</v>
       </c>
       <c r="AD20" t="s">
         <v>252</v>
@@ -8058,10 +8058,10 @@
         <v>365</v>
       </c>
       <c r="AO20">
-        <v>0.99280840617902688</v>
+        <v>0.99864191583933049</v>
       </c>
       <c r="AP20">
-        <v>131.84588671784124</v>
+        <v>24.898209612275185</v>
       </c>
       <c r="AR20" t="s">
         <v>252</v>
@@ -8091,7 +8091,7 @@
         <v>401</v>
       </c>
       <c r="BB20" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="BC20">
         <v>0.98911418404428342</v>
@@ -8162,16 +8162,16 @@
         <v>275</v>
       </c>
       <c r="Y21" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="Z21" t="s">
         <v>315</v>
       </c>
       <c r="AA21">
-        <v>0.99467655833764279</v>
+        <v>0.99865759005097554</v>
       </c>
       <c r="AB21">
-        <v>97.596430476549543</v>
+        <v>24.610849065449354</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -8236,16 +8236,16 @@
         <v>277</v>
       </c>
       <c r="Y22" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="Z22" t="s">
         <v>316</v>
       </c>
       <c r="AA22">
-        <v>0.9926575422237528</v>
+        <v>0.99852761354689235</v>
       </c>
       <c r="AB22">
-        <v>134.61172589786466</v>
+        <v>26.993751640306677</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -8310,16 +8310,16 @@
         <v>279</v>
       </c>
       <c r="Y23" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="Z23" t="s">
         <v>317</v>
       </c>
       <c r="AA23">
-        <v>0.99575198492146944</v>
+        <v>0.99923097127788529</v>
       </c>
       <c r="AB23">
-        <v>77.880276439726259</v>
+        <v>14.098859905436759</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -8384,16 +8384,16 @@
         <v>281</v>
       </c>
       <c r="Y24" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="Z24" t="s">
         <v>318</v>
       </c>
       <c r="AA24">
-        <v>0.99826848327331441</v>
+        <v>0.9962892556180547</v>
       </c>
       <c r="AB24">
-        <v>31.744473322568744</v>
+        <v>68.030313668996456</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -8458,16 +8458,16 @@
         <v>283</v>
       </c>
       <c r="Y25" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="Z25" t="s">
         <v>319</v>
       </c>
       <c r="AA25">
-        <v>0.99619128162656045</v>
+        <v>0.9976124130534012</v>
       </c>
       <c r="AB25">
-        <v>69.826503513057588</v>
+        <v>43.772427354311056</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -8532,16 +8532,16 @@
         <v>285</v>
       </c>
       <c r="Y26" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="Z26" t="s">
         <v>320</v>
       </c>
       <c r="AA26">
-        <v>0.9962892556180547</v>
+        <v>0.9940167733084464</v>
       </c>
       <c r="AB26">
-        <v>68.030313668996456</v>
+        <v>109.69248934514933</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -8606,16 +8606,16 @@
         <v>287</v>
       </c>
       <c r="Y27" t="s">
-        <v>239</v>
+        <v>227</v>
       </c>
       <c r="Z27" t="s">
         <v>321</v>
       </c>
       <c r="AA27">
-        <v>0.9976124130534012</v>
+        <v>0.99765671233232012</v>
       </c>
       <c r="AB27">
-        <v>43.772427354311056</v>
+        <v>42.960273907465258</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -8680,16 +8680,16 @@
         <v>289</v>
       </c>
       <c r="Y28" t="s">
-        <v>227</v>
+        <v>243</v>
       </c>
       <c r="Z28" t="s">
         <v>322</v>
       </c>
       <c r="AA28">
-        <v>0.99765671233232012</v>
+        <v>0.99689028832030402</v>
       </c>
       <c r="AB28">
-        <v>42.960273907465258</v>
+        <v>57.011380794425911</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -8754,16 +8754,16 @@
         <v>291</v>
       </c>
       <c r="Y29" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="Z29" t="s">
         <v>323</v>
       </c>
       <c r="AA29">
-        <v>0.99689028832030402</v>
+        <v>0.9926575422237528</v>
       </c>
       <c r="AB29">
-        <v>57.011380794425911</v>
+        <v>134.61172589786466</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -8828,16 +8828,16 @@
         <v>293</v>
       </c>
       <c r="Y30" t="s">
-        <v>228</v>
+        <v>244</v>
       </c>
       <c r="Z30" t="s">
         <v>324</v>
       </c>
       <c r="AA30">
-        <v>0.99799805381298523</v>
+        <v>0.99858790335879577</v>
       </c>
       <c r="AB30">
-        <v>36.70234676193683</v>
+        <v>25.888438422076831</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -8902,16 +8902,16 @@
         <v>295</v>
       </c>
       <c r="Y31" t="s">
-        <v>250</v>
+        <v>233</v>
       </c>
       <c r="Z31" t="s">
         <v>325</v>
       </c>
       <c r="AA31">
-        <v>0.9980696486807239</v>
+        <v>0.99832758042474679</v>
       </c>
       <c r="AB31">
-        <v>35.389774186729234</v>
+        <v>30.661025546308895</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -8976,16 +8976,16 @@
         <v>297</v>
       </c>
       <c r="Y32" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Z32" t="s">
         <v>326</v>
       </c>
       <c r="AA32">
-        <v>0.99314549576336597</v>
+        <v>0.99610860481200558</v>
       </c>
       <c r="AB32">
-        <v>125.66591100495808</v>
+        <v>71.342245113231982</v>
       </c>
     </row>
     <row r="33" spans="2:28">
@@ -9050,16 +9050,16 @@
         <v>299</v>
       </c>
       <c r="Y33" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Z33" t="s">
         <v>327</v>
       </c>
       <c r="AA33">
-        <v>0.99865759005097554</v>
+        <v>0.99826848327331441</v>
       </c>
       <c r="AB33">
-        <v>24.610849065449354</v>
+        <v>31.744473322568744</v>
       </c>
     </row>
     <row r="34" spans="2:28">
@@ -9124,16 +9124,16 @@
         <v>301</v>
       </c>
       <c r="Y34" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="Z34" t="s">
         <v>328</v>
       </c>
       <c r="AA34">
-        <v>0.99852761354689235</v>
+        <v>0.99619128162656045</v>
       </c>
       <c r="AB34">
-        <v>26.993751640306677</v>
+        <v>69.826503513057588</v>
       </c>
     </row>
   </sheetData>
@@ -9142,7 +9142,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02D490F2-9CDD-4EB1-97C7-0705D3159855}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70F03ADC-0A08-4C6D-B8CF-7939D1651DD1}">
   <dimension ref="B9:Z20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -9254,7 +9254,7 @@
         <v>402</v>
       </c>
       <c r="K11" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="L11">
         <v>0.23246532253847452</v>
@@ -9322,7 +9322,7 @@
         <v>404</v>
       </c>
       <c r="K12" t="s">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="L12">
         <v>4.0336244940056304E-2</v>
@@ -9355,7 +9355,7 @@
         <v>424</v>
       </c>
       <c r="X12" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="Y12">
         <v>1.0927500000000001</v>
@@ -9390,7 +9390,7 @@
         <v>406</v>
       </c>
       <c r="K13" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="L13">
         <v>0.84033275315984202</v>
@@ -9458,7 +9458,7 @@
         <v>408</v>
       </c>
       <c r="K14" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="L14">
         <v>1.0872903918273968</v>
@@ -9491,7 +9491,7 @@
         <v>428</v>
       </c>
       <c r="X14" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="Y14">
         <v>7.6124999999999998</v>
@@ -9526,7 +9526,7 @@
         <v>410</v>
       </c>
       <c r="K15" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="L15">
         <v>0.41379018787058752</v>
@@ -9594,7 +9594,7 @@
         <v>412</v>
       </c>
       <c r="K16" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="L16">
         <v>0.22566824167830141</v>
@@ -9627,7 +9627,7 @@
         <v>432</v>
       </c>
       <c r="X16" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="Y16">
         <v>2.4397500000000001</v>
@@ -9662,7 +9662,7 @@
         <v>414</v>
       </c>
       <c r="K17" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="L17">
         <v>0.79119197542061592</v>
@@ -9695,7 +9695,7 @@
         <v>434</v>
       </c>
       <c r="X17" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="Y17">
         <v>0.189</v>
@@ -9730,7 +9730,7 @@
         <v>416</v>
       </c>
       <c r="K18" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="L18">
         <v>0.24323366751388889</v>
@@ -9763,7 +9763,7 @@
         <v>436</v>
       </c>
       <c r="X18" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="Y18">
         <v>5.9077500000000001</v>
@@ -9798,7 +9798,7 @@
         <v>418</v>
       </c>
       <c r="K19" t="s">
-        <v>364</v>
+        <v>349</v>
       </c>
       <c r="L19">
         <v>0.17228445655487193</v>
@@ -9831,7 +9831,7 @@
         <v>438</v>
       </c>
       <c r="X19" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="Y19">
         <v>3.9195000000000002</v>
@@ -9866,7 +9866,7 @@
         <v>420</v>
       </c>
       <c r="K20" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="L20">
         <v>0.42007398105454308</v>
@@ -9914,7 +9914,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92D2B57F-F811-4000-A366-E5C2E68A912B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54D95C2C-A232-42CD-8A37-A2A000E562E8}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -11731,7 +11731,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F871024-BAD5-4181-8195-25939F7E8630}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A364DC45-B7AB-4A9E-A44B-B605B0C221D3}">
   <dimension ref="B2:M25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
